--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,183 +495,225 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>142256</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13946.67</t>
+          <t>143916</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14109.41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>13946.67</t>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14109.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,183 +537,225 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>143916</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14109.41</t>
+          <t>193716</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18991.76</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14109.41</t>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>18991.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -147,7 +147,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,183 +579,225 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>193716</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18991.76</t>
+          <t>213636</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20944.71</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>18991.76</t>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20944.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,183 +621,225 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>suosuosuoxueerdai</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>213636</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20944.71</t>
+          <t>263436</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25827.06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>20944.71</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>25827.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -231,7 +231,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,183 +663,225 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>263436</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25827.06</t>
+          <t>313236</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30709.41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>25827.06</t>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>30709.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/20 14:40:03</t>
+          <t>09/28 14:18:59</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>3417.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,7 +117,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -273,7 +273,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,183 +705,225 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>313236</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30709.41</t>
+          <t>348096</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34127.06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>30709.41</t>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>34127.06</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 14:18:59</t>
+          <t>09/29 14:15:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3417.65</t>
+          <t>3582.35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/20 14:40:03</t>
+          <t>09/28 14:18:59</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>3417.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,7 +159,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -747,183 +747,225 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>348096</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>34127.06</t>
+          <t>384636</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37709.41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>34127.06</t>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>37709.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 14:15:43</t>
+          <t>10/05 13:27:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3582.35</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/28 14:18:59</t>
+          <t>09/29 14:15:43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3417.65</t>
+          <t>3582.35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/20 14:40:03</t>
+          <t>09/28 14:18:59</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>3417.65</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,7 +201,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -357,7 +357,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,7 +411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -789,183 +789,225 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>384636</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>37709.41</t>
+          <t>407076</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39909.41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>37709.41</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>39909.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/05 13:27:32</t>
+          <t>10/08 10:31:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>4423.53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09/29 14:15:43</t>
+          <t>10/05 13:27:32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3582.35</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/28 14:18:59</t>
+          <t>09/29 14:15:43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3417.65</t>
+          <t>3582.35</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/20 14:40:03</t>
+          <t>09/28 14:18:59</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>3417.65</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,7 +789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -831,183 +831,225 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>407076</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>39909.41</t>
+          <t>452196</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44332.94</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>39909.41</t>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>44332.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/08 10:31:09</t>
+          <t>10/12 17:30:51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4423.53</t>
+          <t>2935.29</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/05 13:27:32</t>
+          <t>10/08 10:31:09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>4423.53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09/29 14:15:43</t>
+          <t>10/05 13:27:32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3582.35</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/28 14:18:59</t>
+          <t>09/29 14:15:43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3417.65</t>
+          <t>3582.35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/20 14:40:03</t>
+          <t>09/28 14:18:59</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>3417.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,7 +285,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -873,183 +873,225 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>452196</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>44332.94</t>
+          <t>482136</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47268.24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>44332.94</t>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>47268.24</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
+++ b/bills/JXZFSP01/-4765454021/9f7c1326fc4776705ce341f528f0ff0b2eabf1f5980195bae4cb054583e8348a/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/12 17:30:51</t>
+          <t>10/15 10:11:05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29940</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2935.29</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10/08 10:31:09</t>
+          <t>10/12 17:30:51</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>29940</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -137,7 +137,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4423.53</t>
+          <t>2935.29</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10/05 13:27:32</t>
+          <t>10/08 10:31:09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -179,7 +179,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>4423.53</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09/29 14:15:43</t>
+          <t>10/05 13:27:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -221,7 +221,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3582.35</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,12 +243,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09/28 14:18:59</t>
+          <t>09/29 14:15:43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34860</t>
+          <t>36540</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -263,7 +263,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3417.65</t>
+          <t>3582.35</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09/20 14:40:03</t>
+          <t>09/28 14:18:59</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -305,7 +305,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>3417.65</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,7 +327,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09/20 10:20:58</t>
+          <t>09/20 14:40:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -369,12 +369,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>09/19 10:55:51</t>
+          <t>09/20 10:20:58</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -389,7 +389,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1952.94</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/18 11:31:04</t>
+          <t>09/19 10:55:51</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>49800</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -431,7 +431,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4882.35</t>
+          <t>1952.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/18 10:09:21</t>
+          <t>09/18 11:31:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>49800</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>162.75</t>
+          <t>4882.35</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/04 10:46:12</t>
+          <t>09/18 10:09:21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>162.75</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>suosuosuoxueerdai</t>
+          <t>ws5751</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>09/03 16:08:11</t>
+          <t>09/04 10:46:12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>09/03 13:23:58</t>
+          <t>09/03 16:08:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>393.92</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>09/02 15:00:27</t>
+          <t>09/03 13:23:58</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>976.47</t>
+          <t>393.92</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -663,7 +663,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>09/02 13:13:43</t>
+          <t>09/02 15:00:27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>09/01 16:19:53</t>
+          <t>09/02 13:13:43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>905.88</t>
+          <t>976.47</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ws5751</t>
+          <t>suosuosuoxueerdai</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/31 13:49:59</t>
+          <t>09/01 16:19:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>321.57</t>
+          <t>905.88</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/31 11:52:34</t>
+          <t>08/31 13:49:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9840</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>964.71</t>
+          <t>321.57</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/30 14:25:58</t>
+          <t>08/31 11:52:34</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2894.12</t>
+          <t>964.71</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/30 13:32:00</t>
+          <t>08/30 14:25:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -915,183 +915,225 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>08/30 13:32:00</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>29520</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2894.12</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ws5751</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>08/29 16:10:49</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>16998</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>1666.47</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>suosuosuoxueerdai</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>suosuosuoxueerdai</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>482136</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>47268.24</t>
+          <t>492096</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48244.71</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>47268.24</t>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>48244.71</t>
         </is>
       </c>
     </row>
